--- a/testData/OpenCart_LoginData.xlsx
+++ b/testData/OpenCart_LoginData.xlsx
@@ -3,33 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomationProjects\OpenCartV21\testData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB54804-0F92-4562-9AFE-183EDB0EB3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{603B3DF1-A291-4E1A-A3C0-62E0FA47EA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{B34B9860-19BB-47EB-B9AF-3CFAA3A5343E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B34B9860-19BB-47EB-B9AF-3CFAA3A5343E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -65,19 +50,19 @@
     <t>xyz</t>
   </si>
   <si>
+    <t>pavanoltraining@gmail.com</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>laksh@yahoo.com</t>
+  </si>
+  <si>
     <t>lakshmi</t>
-  </si>
-  <si>
-    <t>pavanoltraining@gmail.com</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>laksh@yahoo.com</t>
-  </si>
-  <si>
-    <t>email</t>
   </si>
 </sst>
 </file>
@@ -467,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A30C0FC5-E25D-4028-9DAF-67DA198E022B}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.6640625" bestFit="1" customWidth="1"/>
@@ -476,10 +461,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
@@ -504,10 +489,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -518,20 +503,20 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>2</v>
@@ -540,15 +525,16 @@
         <v>6</v>
       </c>
     </row>
+    <row r="7" spans="1:3" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{4469A004-0071-4A3F-98C2-4578FF075342}"/>
     <hyperlink ref="B2" r:id="rId2" xr:uid="{81184D56-6ABD-4BF7-B56F-0F4F23FE001A}"/>
     <hyperlink ref="A3" r:id="rId3" xr:uid="{C3ABD0C8-2629-47E5-868B-4968A3256E75}"/>
     <hyperlink ref="A4" r:id="rId4" xr:uid="{DDF2E9CA-47D1-4992-B949-E7B8AB943554}"/>
-    <hyperlink ref="A5" r:id="rId5" xr:uid="{91F76728-F61F-47E4-97F6-07A2DFC04F2C}"/>
-    <hyperlink ref="B6" r:id="rId6" xr:uid="{1C7E6A63-4FBE-4F40-B8A9-F6384138777E}"/>
-    <hyperlink ref="A6" r:id="rId7" xr:uid="{8416D6FE-519E-49CD-8BBB-B3EA90081147}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{1C7E6A63-4FBE-4F40-B8A9-F6384138777E}"/>
+    <hyperlink ref="A6" r:id="rId6" xr:uid="{8416D6FE-519E-49CD-8BBB-B3EA90081147}"/>
+    <hyperlink ref="A5" r:id="rId7" xr:uid="{91F76728-F61F-47E4-97F6-07A2DFC04F2C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
